--- a/Result/profitability/1714.xlsx
+++ b/Result/profitability/1714.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13625</v>
+        <v>0.2075</v>
       </c>
       <c r="N2" t="n">
-        <v>9.74</v>
+        <v>10.93625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1975</v>
+        <v>0.2725</v>
       </c>
       <c r="N3" t="n">
-        <v>9.4375</v>
+        <v>10.51</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2675</v>
+        <v>0.34</v>
       </c>
       <c r="N4" t="n">
-        <v>8.945</v>
+        <v>10.21125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>0.19625</v>
+        <v>0.26375</v>
       </c>
       <c r="N5" t="n">
-        <v>7.7725</v>
+        <v>9.09375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.38</v>
       </c>
       <c r="M6" t="n">
-        <v>0.22875</v>
+        <v>0.29</v>
       </c>
       <c r="N6" t="n">
-        <v>7.452500000000001</v>
+        <v>8.57625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2875</v>
+        <v>0.35375</v>
       </c>
       <c r="N7" t="n">
-        <v>7.13625</v>
+        <v>7.701249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3275</v>
+        <v>0.38125</v>
       </c>
       <c r="N8" t="n">
-        <v>6.3575</v>
+        <v>7.2925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9864</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8017</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1846</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1463</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1458</v>
+      </c>
+      <c r="K75" t="n">
+        <v>647</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.869565217391304</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.479999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.6654804270462633</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.500000000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.296932515337423</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
